--- a/artfynd/A 41028-2025 artfynd.xlsx
+++ b/artfynd/A 41028-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>123420148</v>
       </c>
       <c r="B2" t="n">
-        <v>78546</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -808,12 +803,7 @@
         <v>123420158</v>
       </c>
       <c r="B3" t="n">
-        <v>79428</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -935,15 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123420169</v>
+        <v>123420167</v>
       </c>
       <c r="B4" t="n">
-        <v>79399</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5495</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -951,21 +936,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>101410</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -975,7 +960,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -984,10 +969,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>607959</v>
+        <v>607957</v>
       </c>
       <c r="R4" t="n">
-        <v>6760654</v>
+        <v>6760651</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,7 +999,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_2937</t>
+          <t>2024_2939</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1024,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1034,7 +1019,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1058,6 +1043,131 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123420169</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>S Vitrosmuran, Gstr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>607959</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6760654</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hamrånge</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2024_2937</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
         <is>
           <t>Kustpaketet</t>
         </is>

--- a/artfynd/A 41028-2025 artfynd.xlsx
+++ b/artfynd/A 41028-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -797,6 +802,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123420148</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -922,6 +932,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123420158</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1047,6 +1062,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123420167</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1172,8 +1192,19 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123420169</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>